--- a/01_data_collection/manual_inputs/AI Articles By Company.xlsx
+++ b/01_data_collection/manual_inputs/AI Articles By Company.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmngglobal-my.sharepoint.com/personal/ishan_shah_cartesian_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmngglobal-my.sharepoint.com/personal/ananya_shah_cartesian_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73E92C87-6BA9-4C4D-8D88-AABB2F3636FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36161355-66A5-4559-B4CE-C96049748BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{9B5C895A-4F6E-41AC-9F51-19DF70044AC4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{9B5C895A-4F6E-41AC-9F51-19DF70044AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Company List" sheetId="3" r:id="rId1"/>
     <sheet name="AI Use Case Data" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,407 +62,407 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="132">
   <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Article</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>AI Use Case</t>
+  </si>
+  <si>
+    <t>BT</t>
+  </si>
+  <si>
+    <t>BT Group leans on AI to transform customer service experience</t>
+  </si>
+  <si>
+    <t>Customer Service</t>
+  </si>
+  <si>
+    <t>BT to boost use of AI to reverse declines at business unit</t>
+  </si>
+  <si>
+    <t>Manual Data Processing</t>
+  </si>
+  <si>
+    <t>BT ramps up AI use to counter hacking threats to business customers | BT | The Guardian</t>
+  </si>
+  <si>
+    <t>Cybersecurity</t>
+  </si>
+  <si>
+    <t>BT’s network platform strategy is rooted in AI</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>Why AI and Agile are at the heart of corporate digital transformation at BT Group - a progress report</t>
+  </si>
+  <si>
+    <t>Case study: BT rolls out Amazon’s generative AI developer tool to more coders | Computer Weekly</t>
+  </si>
+  <si>
+    <t>Internal Productivity</t>
+  </si>
+  <si>
+    <t>https://www.fierce-network.com/modernization/bt-vodafone-execs-talk-about-training-their-employees-ai</t>
+  </si>
+  <si>
+    <t>How BT worked to avoid GenAI lock-in</t>
+  </si>
+  <si>
+    <t>Other Notes</t>
+  </si>
+  <si>
+    <t>Platform allows them to use any underlying model</t>
+  </si>
+  <si>
+    <t>Uses a company called sprinklr</t>
+  </si>
+  <si>
+    <t>BT Group’s Digital unit accelerates AI use cases and navigates GenAI</t>
+  </si>
+  <si>
+    <t>Have an AI Accelerator enabling them to launch AI projects within 14 days</t>
+  </si>
+  <si>
+    <t>BT and Pindrop Team Up to Combat Voice Fraud with AI | VoIP Review</t>
+  </si>
+  <si>
+    <t>Fraud Detection / Cybersecurity</t>
+  </si>
+  <si>
+    <t>Comms Business - BT implements AI-enhanced training platform</t>
+  </si>
+  <si>
+    <t>BT Group employs ServiceNow AI to enhance staff operations - Techerati</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>BT partners with Nokia to deliver superior customer experience and improve operational efficiency | Nokia.com</t>
+  </si>
+  <si>
+    <t>AI Ops</t>
+  </si>
+  <si>
+    <t>BT Sourced powers procurement transformation with AI, automation and analytics</t>
+  </si>
+  <si>
+    <t>Procurement</t>
+  </si>
+  <si>
+    <t>Subsidiary focussed on AI procurement</t>
+  </si>
+  <si>
+    <t>Globality and BT Announce New Partnership to Unleash the Power of Procurement</t>
+  </si>
+  <si>
+    <t>VMO2</t>
+  </si>
+  <si>
+    <t>Virgin Media O2 launches new AI tools to supercharge customer services and better help most vulnerable customers - Virgin Media O2</t>
+  </si>
+  <si>
+    <t>Virgin Media O2 deploys AI-powered network intelligence to strengthen broadband service delivery</t>
+  </si>
+  <si>
+    <t>Transforming Risk Management at Virgin Media O2 with Generative AI</t>
+  </si>
+  <si>
+    <t>Risk Reporting</t>
+  </si>
+  <si>
+    <t>Virgin Media O2 rolls out AI training as part of enhanced learning and development programme to equip employees with critical skills - Virgin Media O2</t>
+  </si>
+  <si>
+    <t>Accelerating VMO2’s Network Operations with AI and Automation</t>
+  </si>
+  <si>
+    <t>O2 Business launches new AI technology to improve customer experiences in stores - Virgin Media O2</t>
+  </si>
+  <si>
+    <t>Virgin Media O2 partners with Perplexity for AI search access - CO/AI</t>
+  </si>
+  <si>
+    <t>Selling as Add-On</t>
+  </si>
+  <si>
+    <t>O2 deploys AI granny against scammers • The Register</t>
+  </si>
+  <si>
+    <t>Fraud Detection</t>
+  </si>
+  <si>
+    <t>VMO2 fights spam with Hiya roll-out AI spam fighting tools - Capacity</t>
+  </si>
+  <si>
+    <t>Virgin Media O2 works with EkkoSense to unlock data centre cooling energy savings worth over £1 million per year - Virgin Media O2</t>
+  </si>
+  <si>
+    <t>Data Centre Operations</t>
+  </si>
+  <si>
+    <t>The MLOps Cookbook: how we optimised our Vertex AI Pipelines Environments at VMO2 for scale | by Digital at Virgin Media O2 | Medium</t>
+  </si>
+  <si>
+    <t>Unsure</t>
+  </si>
+  <si>
+    <t>Vodafone</t>
+  </si>
+  <si>
+    <t>Inside Virgin Media O2’s AI Strategy for the Network of the Future</t>
+  </si>
+  <si>
+    <t>How Vodafone is using AI to shape the next generation of customer service</t>
+  </si>
+  <si>
+    <t>How Vodafone is using gen AI to enhance network lifecycle | Google Cloud Blog</t>
+  </si>
+  <si>
+    <t>Vodafone uses robots to screen jobhunters</t>
+  </si>
+  <si>
+    <t>Recruitment</t>
+  </si>
+  <si>
+    <t>Vodafone forecasts ‘big bang’ as agentic AI starts to transform network ops | Technology | TelcoTitans.com</t>
+  </si>
+  <si>
+    <t>How Vodafone plans to create AI-powered tech-comms powerhouse with Microsoft - Microsoft UK Stories</t>
+  </si>
+  <si>
+    <t>KPMG did a trial to show the productivity gains</t>
+  </si>
+  <si>
+    <t>Vodafone and Zinkworks partner to create AI platform to simplify and accelerate launch of new mobile network apps for customers</t>
+  </si>
+  <si>
+    <t>Vodafone eyes service growth from internal AI and IT innovation</t>
+  </si>
+  <si>
+    <t>AI booster program enabling engineers to deploy new models</t>
+  </si>
+  <si>
+    <t>How Vodafone is leveraging AI for competitive advantage</t>
+  </si>
+  <si>
+    <t>Various</t>
+  </si>
+  <si>
+    <t>Highlights a vaierty of benefits / challenges</t>
+  </si>
+  <si>
+    <t>Vodafone calls upon Gen AI to expand use of IT tools - Capgemini</t>
+  </si>
+  <si>
+    <t>Vodafone uses AI to detect and fix network issues | TechRadar</t>
+  </si>
+  <si>
+    <t>aimagazine.com | 500: Internal server error</t>
+  </si>
+  <si>
+    <t>sustainabilitymag.com | 500: Internal server error</t>
+  </si>
+  <si>
+    <t>Vodafone will use AI to help customers who phone its call centre: How will it work? | This is Money</t>
+  </si>
+  <si>
+    <t>Network-as-a-Sensor</t>
+  </si>
+  <si>
     <t>Company List</t>
   </si>
   <si>
+    <t>Personalising the journey to full fibre | CityFibre</t>
+  </si>
+  <si>
+    <t>CityFibre</t>
+  </si>
+  <si>
+    <t>CityFibre and IQGeo customer story | IQGeo</t>
+  </si>
+  <si>
+    <t>Cityfibre prioritizes automation for “friction free” customer journeys</t>
+  </si>
+  <si>
+    <t>Customer Service / Internal Productivity</t>
+  </si>
+  <si>
+    <t>Using AI to power a new era of customer service quality | CityFibre</t>
+  </si>
+  <si>
+    <t>Post | LinkedIn</t>
+  </si>
+  <si>
+    <t>Created a snowflake data cloud to enable AI</t>
+  </si>
+  <si>
+    <t>Sky</t>
+  </si>
+  <si>
+    <t>TalkTalk</t>
+  </si>
+  <si>
+    <t>Sky looks to AI to get smarter about customers - benefits, learnings and cautions</t>
+  </si>
+  <si>
+    <t>Sky flexes its AI muscles</t>
+  </si>
+  <si>
+    <t>Sales / Customer Service</t>
+  </si>
+  <si>
+    <t>Sky turns to AI chatbots, cutting 2,000 call centre jobs - InfotechLead</t>
+  </si>
+  <si>
+    <t>Hosted internal AI Competition</t>
+  </si>
+  <si>
+    <t>Broadband ISP TalkTalk UK Adopt NiCE's AI-Powered Customer Service Platform - ISPreview UK</t>
+  </si>
+  <si>
+    <t>TalkTalk partners with Kraken to revolutionise customer experience for millions of UK broadband customers - TalkTalk Group</t>
+  </si>
+  <si>
+    <t>MD Tech Leader Talks with Phil Haslam, CTO at TalkTalk - The roundup | Manchester Digital</t>
+  </si>
+  <si>
+    <t>Internal Productivity / Network Ops</t>
+  </si>
+  <si>
+    <t>Netomnia</t>
+  </si>
+  <si>
+    <t>nexfibre</t>
+  </si>
+  <si>
+    <t>Hyperoptic</t>
+  </si>
+  <si>
+    <t>Community Fibre</t>
+  </si>
+  <si>
+    <t>FullFibre</t>
+  </si>
+  <si>
+    <t>Gigaclear</t>
+  </si>
+  <si>
+    <t>Created internal platform which unifies all data - Odin</t>
+  </si>
+  <si>
+    <t>No Mentions Identified</t>
+  </si>
+  <si>
+    <t>No mentions in public domain - should caveat that they are owned by VMO2 so in practice would have initatives</t>
+  </si>
+  <si>
+    <t>Customer Service / Hyperpersonalisation</t>
+  </si>
+  <si>
+    <t>Community Fibre partners with Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t>CommunityFibre Adopt AI-Driven Analytics to Improve Home WiFi - ISPreview UK</t>
+  </si>
+  <si>
+    <t>How Community Fibre 12x’d Their Customer Base While Keeping Customer Support Contacts Flat with Yext | Yext</t>
+  </si>
+  <si>
+    <t>AI SEO</t>
+  </si>
+  <si>
+    <t>FullFibre partners with Gigabit IQ</t>
+  </si>
+  <si>
+    <t>Rural UK ISP Gigaclear Adopts AI to Improve Customer Broadband Installs - ISPreview UK</t>
+  </si>
+  <si>
+    <t>Gigaclear adopts the Aiimi Insight Engine - Aiimi</t>
+  </si>
+  <si>
+    <t>Gigaclear | WorkRamp</t>
+  </si>
+  <si>
+    <t>Gigaclear enhances telephony services with Oculeus' RVM</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>Openreach</t>
+  </si>
+  <si>
+    <t>APFN</t>
+  </si>
+  <si>
+    <t>ITS</t>
+  </si>
+  <si>
+    <t>Openreach AI Chatbots and Data Analytics Aid Network Management - ISPreview UK</t>
+  </si>
+  <si>
+    <t>Openreach turns to video AI to cut install snags | Operations | TelcoTitans.com</t>
+  </si>
+  <si>
+    <t>Openreach-Annual-Review-2023 online.pdf</t>
+  </si>
+  <si>
+    <t>No mentions in public domain</t>
+  </si>
+  <si>
+    <t>Zen</t>
+  </si>
+  <si>
+    <t>Glide</t>
+  </si>
+  <si>
+    <t>Utility Warehouse</t>
+  </si>
+  <si>
+    <t>Cuckoo</t>
+  </si>
+  <si>
+    <t>YouFibre / Brsk</t>
+  </si>
+  <si>
+    <t>Introducing Beni: Advanced AI Integration for Zen Internet Customer Support | CBM Digital</t>
+  </si>
+  <si>
+    <t>Utility Warehouse Case Study  |  Google Cloud Documentation</t>
+  </si>
+  <si>
+    <t>AI / ML</t>
+  </si>
+  <si>
+    <t>Utility Warehouse streamlines success</t>
+  </si>
+  <si>
+    <t>Brsk launches WhatsApp chat support | thinkbroadband</t>
+  </si>
+  <si>
     <t>Company Type</t>
   </si>
   <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Article</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>AI Use Case</t>
-  </si>
-  <si>
-    <t>Other Notes</t>
-  </si>
-  <si>
     <t>ISP</t>
   </si>
   <si>
-    <t>BT</t>
-  </si>
-  <si>
-    <t>BT Group leans on AI to transform customer service experience</t>
-  </si>
-  <si>
-    <t>Customer Service</t>
-  </si>
-  <si>
-    <t>Uses a company called sprinklr</t>
-  </si>
-  <si>
-    <t>BT to boost use of AI to reverse declines at business unit</t>
-  </si>
-  <si>
-    <t>Manual Data Processing</t>
-  </si>
-  <si>
-    <t>BT ramps up AI use to counter hacking threats to business customers | BT | The Guardian</t>
-  </si>
-  <si>
-    <t>Cybersecurity</t>
-  </si>
-  <si>
-    <t>BT’s network platform strategy is rooted in AI</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>Why AI and Agile are at the heart of corporate digital transformation at BT Group - a progress report</t>
-  </si>
-  <si>
-    <t>Case study: BT rolls out Amazon’s generative AI developer tool to more coders | Computer Weekly</t>
-  </si>
-  <si>
-    <t>Internal Productivity</t>
-  </si>
-  <si>
-    <t>https://www.fierce-network.com/modernization/bt-vodafone-execs-talk-about-training-their-employees-ai</t>
-  </si>
-  <si>
-    <t>How BT worked to avoid GenAI lock-in</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Platform allows them to use any underlying model</t>
-  </si>
-  <si>
-    <t>BT Group’s Digital unit accelerates AI use cases and navigates GenAI</t>
-  </si>
-  <si>
-    <t>Have an AI Accelerator enabling them to launch AI projects within 14 days</t>
-  </si>
-  <si>
-    <t>BT and Pindrop Team Up to Combat Voice Fraud with AI | VoIP Review</t>
-  </si>
-  <si>
-    <t>Fraud Detection / Cybersecurity</t>
-  </si>
-  <si>
-    <t>Comms Business - BT implements AI-enhanced training platform</t>
-  </si>
-  <si>
-    <t>BT Group employs ServiceNow AI to enhance staff operations - Techerati</t>
-  </si>
-  <si>
-    <t>BT partners with Nokia to deliver superior customer experience and improve operational efficiency | Nokia.com</t>
-  </si>
-  <si>
-    <t>BT Sourced powers procurement transformation with AI, automation and analytics</t>
-  </si>
-  <si>
-    <t>Procurement</t>
-  </si>
-  <si>
-    <t>Subsidiary focussed on AI procurement</t>
-  </si>
-  <si>
-    <t>Globality and BT Announce New Partnership to Unleash the Power of Procurement</t>
-  </si>
-  <si>
-    <t>VMO2</t>
-  </si>
-  <si>
-    <t>Virgin Media O2 launches new AI tools to supercharge customer services and better help most vulnerable customers - Virgin Media O2</t>
-  </si>
-  <si>
-    <t>Virgin Media O2 deploys AI-powered network intelligence to strengthen broadband service delivery</t>
-  </si>
-  <si>
-    <t>Transforming Risk Management at Virgin Media O2 with Generative AI</t>
-  </si>
-  <si>
-    <t>Risk Reporting</t>
-  </si>
-  <si>
-    <t>Virgin Media O2 rolls out AI training as part of enhanced learning and development programme to equip employees with critical skills - Virgin Media O2</t>
-  </si>
-  <si>
-    <t>Accelerating VMO2’s Network Operations with AI and Automation</t>
-  </si>
-  <si>
-    <t>O2 Business launches new AI technology to improve customer experiences in stores - Virgin Media O2</t>
-  </si>
-  <si>
-    <t>Virgin Media O2 partners with Perplexity for AI search access - CO/AI</t>
-  </si>
-  <si>
-    <t>Selling as Add-On</t>
-  </si>
-  <si>
-    <t>O2 deploys AI granny against scammers • The Register</t>
-  </si>
-  <si>
-    <t>Fraud Detection</t>
-  </si>
-  <si>
-    <t>VMO2 fights spam with Hiya roll-out AI spam fighting tools - Capacity</t>
-  </si>
-  <si>
-    <t>Virgin Media O2 works with EkkoSense to unlock data centre cooling energy savings worth over £1 million per year - Virgin Media O2</t>
-  </si>
-  <si>
-    <t>Data Centre Operations</t>
-  </si>
-  <si>
-    <t>The MLOps Cookbook: how we optimised our Vertex AI Pipelines Environments at VMO2 for scale | by Digital at Virgin Media O2 | Medium</t>
-  </si>
-  <si>
-    <t>Unsure</t>
-  </si>
-  <si>
-    <t>Inside Virgin Media O2’s AI Strategy for the Network of the Future</t>
-  </si>
-  <si>
-    <t>AI Ops</t>
-  </si>
-  <si>
-    <t>Vodafone</t>
-  </si>
-  <si>
-    <t>How Vodafone is using AI to shape the next generation of customer service</t>
-  </si>
-  <si>
-    <t>How Vodafone is using gen AI to enhance network lifecycle | Google Cloud Blog</t>
-  </si>
-  <si>
-    <t>Vodafone uses robots to screen jobhunters</t>
-  </si>
-  <si>
-    <t>Recruitment</t>
-  </si>
-  <si>
-    <t>Vodafone forecasts ‘big bang’ as agentic AI starts to transform network ops | Technology | TelcoTitans.com</t>
-  </si>
-  <si>
-    <t>How Vodafone plans to create AI-powered tech-comms powerhouse with Microsoft - Microsoft UK Stories</t>
-  </si>
-  <si>
-    <t>KPMG did a trial to show the productivity gains</t>
-  </si>
-  <si>
-    <t>Vodafone and Zinkworks partner to create AI platform to simplify and accelerate launch of new mobile network apps for customers</t>
-  </si>
-  <si>
-    <t>Vodafone eyes service growth from internal AI and IT innovation</t>
-  </si>
-  <si>
-    <t>AI booster program enabling engineers to deploy new models</t>
-  </si>
-  <si>
-    <t>How Vodafone is leveraging AI for competitive advantage</t>
-  </si>
-  <si>
-    <t>Various</t>
-  </si>
-  <si>
-    <t>Highlights a vaierty of benefits / challenges</t>
-  </si>
-  <si>
-    <t>Vodafone calls upon Gen AI to expand use of IT tools - Capgemini</t>
-  </si>
-  <si>
-    <t>Vodafone uses AI to detect and fix network issues | TechRadar</t>
-  </si>
-  <si>
-    <t>aimagazine.com | 500: Internal server error</t>
-  </si>
-  <si>
-    <t>sustainabilitymag.com | 500: Internal server error</t>
-  </si>
-  <si>
-    <t>Network-as-a-Sensor</t>
-  </si>
-  <si>
-    <t>Vodafone will use AI to help customers who phone its call centre: How will it work? | This is Money</t>
-  </si>
-  <si>
-    <t>Sky</t>
-  </si>
-  <si>
-    <t>Sky looks to AI to get smarter about customers - benefits, learnings and cautions</t>
-  </si>
-  <si>
-    <t>Sky flexes its AI muscles</t>
-  </si>
-  <si>
-    <t>Sales / Customer Service</t>
-  </si>
-  <si>
-    <t>Sky turns to AI chatbots, cutting 2,000 call centre jobs - InfotechLead</t>
-  </si>
-  <si>
-    <t>Post | LinkedIn</t>
-  </si>
-  <si>
-    <t>Hosted internal AI Competition</t>
-  </si>
-  <si>
-    <t>TalkTalk</t>
-  </si>
-  <si>
-    <t>Broadband ISP TalkTalk UK Adopt NiCE's AI-Powered Customer Service Platform - ISPreview UK</t>
-  </si>
-  <si>
-    <t>TalkTalk partners with Kraken to revolutionise customer experience for millions of UK broadband customers - TalkTalk Group</t>
-  </si>
-  <si>
-    <t>MD Tech Leader Talks with Phil Haslam, CTO at TalkTalk - The roundup | Manchester Digital</t>
-  </si>
-  <si>
-    <t>Internal Productivity / Network Ops</t>
-  </si>
-  <si>
-    <t>Personalising the journey to full fibre | CityFibre</t>
-  </si>
-  <si>
-    <t>Glide</t>
-  </si>
-  <si>
-    <t>No Mentions Identified</t>
-  </si>
-  <si>
-    <t>No mentions in public domain</t>
-  </si>
-  <si>
-    <t>Zen</t>
-  </si>
-  <si>
-    <t>Introducing Beni: Advanced AI Integration for Zen Internet Customer Support | CBM Digital</t>
-  </si>
-  <si>
-    <t>Utility Warehouse</t>
-  </si>
-  <si>
-    <t>Utility Warehouse Case Study  |  Google Cloud Documentation</t>
-  </si>
-  <si>
-    <t>AI / ML</t>
-  </si>
-  <si>
-    <t>Utility Warehouse streamlines success</t>
-  </si>
-  <si>
-    <t>Cuckoo</t>
-  </si>
-  <si>
-    <t>YouFibre / Brsk</t>
-  </si>
-  <si>
-    <t>Brsk launches WhatsApp chat support | thinkbroadband</t>
-  </si>
-  <si>
     <t>Infra Companies</t>
-  </si>
-  <si>
-    <t>Openreach</t>
-  </si>
-  <si>
-    <t>Openreach AI Chatbots and Data Analytics Aid Network Management - ISPreview UK</t>
-  </si>
-  <si>
-    <t>Openreach turns to video AI to cut install snags | Operations | TelcoTitans.com</t>
-  </si>
-  <si>
-    <t>Openreach-Annual-Review-2023 online.pdf</t>
-  </si>
-  <si>
-    <t>CityFibre</t>
-  </si>
-  <si>
-    <t>CityFibre and IQGeo customer story | IQGeo</t>
-  </si>
-  <si>
-    <t>Cityfibre prioritizes automation for “friction free” customer journeys</t>
-  </si>
-  <si>
-    <t>Customer Service / Internal Productivity</t>
-  </si>
-  <si>
-    <t>Using AI to power a new era of customer service quality | CityFibre</t>
-  </si>
-  <si>
-    <t>Created a snowflake data cloud to enable AI</t>
-  </si>
-  <si>
-    <t>Netomnia</t>
-  </si>
-  <si>
-    <t>Created internal platform which unifies all data - Odin</t>
-  </si>
-  <si>
-    <t>nexfibre</t>
-  </si>
-  <si>
-    <t>No mentions in public domain - should caveat that they are owned by VMO2 so in practice would have initatives</t>
-  </si>
-  <si>
-    <t>Hyperoptic</t>
-  </si>
-  <si>
-    <t>Customer Service / Hyperpersonalisation</t>
-  </si>
-  <si>
-    <t>Community Fibre</t>
-  </si>
-  <si>
-    <t>Community Fibre partners with Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t>CommunityFibre Adopt AI-Driven Analytics to Improve Home WiFi - ISPreview UK</t>
-  </si>
-  <si>
-    <t>How Community Fibre 12x’d Their Customer Base While Keeping Customer Support Contacts Flat with Yext | Yext</t>
-  </si>
-  <si>
-    <t>AI SEO</t>
-  </si>
-  <si>
-    <t>FullFibre</t>
-  </si>
-  <si>
-    <t>FullFibre partners with Gigabit IQ</t>
-  </si>
-  <si>
-    <t>Gigaclear</t>
-  </si>
-  <si>
-    <t>Rural UK ISP Gigaclear Adopts AI to Improve Customer Broadband Installs - ISPreview UK</t>
-  </si>
-  <si>
-    <t>Gigaclear adopts the Aiimi Insight Engine - Aiimi</t>
-  </si>
-  <si>
-    <t>Compliance</t>
-  </si>
-  <si>
-    <t>Gigaclear | WorkRamp</t>
-  </si>
-  <si>
-    <t>Gigaclear enhances telephony services with Oculeus' RVM</t>
-  </si>
-  <si>
-    <t>APFN</t>
-  </si>
-  <si>
-    <t>ITS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -920,535 +921,535 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB577DD-80B1-437E-9CC5-FAA342799AF1}">
   <dimension ref="A1:A161"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="str" cm="1">
         <f t="array" ref="A2:A21">_xlfn.UNIQUE(Table1[Company])</f>
         <v>BT</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="str">
         <v>VMO2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="str">
         <v>Vodafone</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="str">
         <v>Sky</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="str">
         <v>TalkTalk</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="str">
         <v>Glide</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="str">
         <v>Zen</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="str">
         <v>Utility Warehouse</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="str">
         <v>Cuckoo</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="str">
         <v>YouFibre / Brsk</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="str">
         <v>Openreach</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="str">
         <v>CityFibre</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="str">
         <v>Netomnia</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="str">
         <v>nexfibre</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="str">
         <v>Hyperoptic</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="str">
         <v>Community Fibre</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="str">
         <v>FullFibre</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="str">
         <v>Gigaclear</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="str">
         <v>APFN</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="str">
         <v>ITS</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" s="1"/>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" s="1"/>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" s="1"/>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" s="1"/>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" s="1"/>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" s="1"/>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" s="1"/>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" s="1"/>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" s="1"/>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" s="1"/>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" s="1"/>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" s="1"/>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" s="1"/>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" s="1"/>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" s="1"/>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" s="1"/>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" s="1"/>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" s="1"/>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" s="1"/>
     </row>
-    <row r="111" spans="1:1">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" s="1"/>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" s="1"/>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" s="1"/>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" s="1"/>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" s="1"/>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" s="1"/>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" s="1"/>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" s="1"/>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" s="1"/>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" s="1"/>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" s="1"/>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" s="1"/>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" s="1"/>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" s="1"/>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" s="1"/>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" s="1"/>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" s="1"/>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" s="1"/>
     </row>
-    <row r="129" spans="1:1">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" s="1"/>
     </row>
-    <row r="130" spans="1:1">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" s="1"/>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" s="1"/>
     </row>
-    <row r="132" spans="1:1">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132" s="1"/>
     </row>
-    <row r="133" spans="1:1">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133" s="1"/>
     </row>
-    <row r="134" spans="1:1">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134" s="1"/>
     </row>
-    <row r="135" spans="1:1">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135" s="1"/>
     </row>
-    <row r="136" spans="1:1">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136" s="1"/>
     </row>
-    <row r="137" spans="1:1">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" s="1"/>
     </row>
-    <row r="138" spans="1:1">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138" s="1"/>
     </row>
-    <row r="139" spans="1:1">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" s="1"/>
     </row>
-    <row r="140" spans="1:1">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140" s="1"/>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" s="1"/>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142" s="1"/>
     </row>
-    <row r="143" spans="1:1">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143" s="1"/>
     </row>
-    <row r="144" spans="1:1">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144" s="1"/>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" s="1"/>
     </row>
-    <row r="146" spans="1:1">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146" s="1"/>
     </row>
-    <row r="147" spans="1:1">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147" s="1"/>
     </row>
-    <row r="148" spans="1:1">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148" s="1"/>
     </row>
-    <row r="149" spans="1:1">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" s="1"/>
     </row>
-    <row r="150" spans="1:1">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150" s="1"/>
     </row>
-    <row r="151" spans="1:1">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" s="1"/>
     </row>
-    <row r="152" spans="1:1">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152" s="1"/>
     </row>
-    <row r="153" spans="1:1">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" s="1"/>
     </row>
-    <row r="154" spans="1:1">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154" s="1"/>
     </row>
-    <row r="155" spans="1:1">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" s="1"/>
     </row>
-    <row r="156" spans="1:1">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156" s="1"/>
     </row>
-    <row r="157" spans="1:1">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" s="1"/>
     </row>
-    <row r="158" spans="1:1">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158" s="1"/>
     </row>
-    <row r="159" spans="1:1">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" s="1"/>
     </row>
-    <row r="160" spans="1:1">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160" s="1"/>
     </row>
-    <row r="161" spans="1:1">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" s="1"/>
     </row>
   </sheetData>
@@ -1459,1405 +1460,1405 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BBB1250-B694-44EF-957F-C7F3B858F4EC}">
   <dimension ref="A1:F79"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="130.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="96.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.54296875" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="130.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="96.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="5">
         <v>45627</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="5">
         <v>45962</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D4" s="5">
         <v>45413</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5">
         <v>45566</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5">
         <v>45292</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D7" s="5">
         <v>45444</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D8" s="5">
         <v>45809</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D9" s="5">
         <v>45536</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D10" s="5">
         <v>45108</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D11" s="5">
         <v>45962</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D12" s="5">
         <v>45413</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D13" s="5">
         <v>45444</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" s="5">
         <v>45017</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="F15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="D16" s="5">
         <v>45323</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" s="5">
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="D18" s="5">
         <v>45901</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D19" s="5">
         <v>45717</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D20" s="5">
         <v>45689</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D21" s="5">
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D22" s="5">
         <v>44378</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D23" s="5">
         <v>45597</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D24" s="5">
         <v>45597</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D25" s="5">
         <v>45323</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="D26" s="5">
         <v>45536</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D27" s="5">
         <v>44986</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D28" s="5">
         <v>45931</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D29" s="5">
         <v>45566</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D30" s="5">
         <v>45597</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D31" s="5">
         <v>45809</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="D32" s="5">
         <v>42887</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D33" s="5">
         <v>45748</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D34" s="5">
         <v>45536</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D35" s="5">
         <v>45931</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D36" s="5">
         <v>45748</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D37" s="5">
         <v>45383</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F37" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="D39" s="5">
         <v>44378</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D40" s="5">
         <v>45870</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D41" s="5">
         <v>45809</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D42" s="5">
         <v>45566</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D43" s="5">
         <v>43221</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D44" s="5">
         <v>43405</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D45" s="5">
         <v>45748</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D46" s="5">
         <v>45839</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F46" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D47" s="5">
         <v>45839</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D48" s="5">
         <v>45748</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D50" s="5">
         <v>45017</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F51" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D52" s="5">
         <v>45413</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D56" s="5">
         <v>45870</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="D57" s="5">
         <v>45444</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D58" s="5">
         <v>43497</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D59" s="5">
         <v>44562</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D60" s="5">
         <v>45931</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D61" s="5">
         <v>45261</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D62" s="5">
         <v>45017</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="D64" s="5">
         <v>45139</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="D65" s="5">
         <v>44835</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D66" s="5">
         <v>45597</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F66" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D67" s="5">
         <v>45962</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F67" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F68" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D69" s="5">
         <v>45931</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D70" s="5">
         <v>45170</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D71" s="5">
         <v>44409</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D73" s="5">
         <v>45689</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D74" s="5">
         <v>45901</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D75" s="5">
         <v>44986</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D77" s="5">
         <v>45231</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F78" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F79" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
